--- a/data/trans_camb/P1410-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1410-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,07</t>
+          <t>-0,36; 1,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,48</t>
+          <t>-0,19; 1,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,46</t>
+          <t>-0,38; 4,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,51</t>
+          <t>0,03; 2,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,8</t>
+          <t>-0,12; 1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,33</t>
+          <t>-0,37; 3,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,31</t>
+          <t>0,04; 1,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,13</t>
+          <t>-0,06; 1,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,05</t>
+          <t>-0,19; 2,53</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>469,52%</t>
+          <t>362,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>353,37%</t>
+          <t>350,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>419,25%</t>
+          <t>357,07%</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-52,78; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,51</t>
+          <t>-0,63; 0,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; -0,12</t>
+          <t>-1,15; -0,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,72</t>
+          <t>-0,5; 1,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,48</t>
+          <t>-0,8; 0,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,21</t>
+          <t>-0,55; 1,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,34</t>
+          <t>-0,59; 1,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,34</t>
+          <t>-0,54; 0,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,4</t>
+          <t>-0,5; 0,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,08</t>
+          <t>-0,41; 0,89</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,06; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,08; 218,01</t>
+          <t>-85,74; 194,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,77; 318,58</t>
+          <t>-83,61; 261,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 634,98</t>
+          <t>-74,43; 511,74</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 1,7</t>
+          <t>0,01; 1,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,58</t>
+          <t>-0,57; 0,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,18</t>
+          <t>-0,08; 1,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,38</t>
+          <t>-1,11; 1,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,81</t>
+          <t>-1,44; 0,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,35</t>
+          <t>-1,72; 0,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,23</t>
+          <t>-0,4; 1,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,55</t>
+          <t>-0,76; 0,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,86</t>
+          <t>-0,65; 0,87</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>279,86%</t>
+          <t>234,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-47,6%</t>
+          <t>-38,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,21; —</t>
+          <t>-40,15; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,6; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 208,94</t>
+          <t>-63,58; 173,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 124,19</t>
+          <t>-75,93; 127,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,22; 72,65</t>
+          <t>-83,36; 71,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 259,25</t>
+          <t>-34,62; 261,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,01; 108,89</t>
+          <t>-66,74; 127,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 202,57</t>
+          <t>-53,86; 173,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>0,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,08</t>
+          <t>-2,8; 1,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 0,65</t>
+          <t>-3,06; 0,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 1,38</t>
+          <t>-1,91; 2,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,07</t>
+          <t>-3,17; -0,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,81</t>
+          <t>-1,76; 1,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,03</t>
+          <t>-1,72; 1,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,08</t>
+          <t>-2,46; 0,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,93</t>
+          <t>-1,79; 0,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,77</t>
+          <t>-1,25; 1,31</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-22,16%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-14,38%</t>
+          <t>-5,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-18,17%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 65,24</t>
+          <t>-70,53; 74,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,05; 40,81</t>
+          <t>-70,98; 48,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,42; 62,9</t>
+          <t>-48,08; 114,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-89,69; 21,24</t>
+          <t>-91,44; 9,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 123,0</t>
+          <t>-52,69; 135,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,89; 72,2</t>
+          <t>-48,95; 108,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-73,1; 10,53</t>
+          <t>-73,07; 5,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,78; 53,74</t>
+          <t>-52,17; 53,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 38,33</t>
+          <t>-37,98; 61,99</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,18</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-1,67</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-1,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -1,67</t>
+          <t>-9,27; -1,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -1,16</t>
+          <t>-9,63; -1,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 1,69</t>
+          <t>-6,29; 1,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,92</t>
+          <t>-2,37; 4,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1,05</t>
+          <t>-4,48; 1,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,6</t>
+          <t>-4,41; 0,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,11</t>
+          <t>-5,03; 0,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -0,86</t>
+          <t>-5,6; -0,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,26</t>
+          <t>-4,16; 0,46</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-20,13%</t>
+          <t>-20,45%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-35,18%</t>
+          <t>-33,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-23,73%</t>
+          <t>-23,93%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,75; -17,42</t>
+          <t>-70,4; -19,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-66,96; -8,08</t>
+          <t>-68,36; -12,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 19,72</t>
+          <t>-45,29; 18,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 120,08</t>
+          <t>-36,13; 131,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,12; 33,52</t>
+          <t>-65,19; 43,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 22,86</t>
+          <t>-62,89; 24,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,72; 1,71</t>
+          <t>-52,42; 1,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-61,54; -12,49</t>
+          <t>-59,54; -11,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-45,68; 5,4</t>
+          <t>-45,53; 7,53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-4,5</t>
+          <t>-4,92</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,2</t>
+          <t>-1,84</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-4,79</t>
+          <t>-3,2</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 1,03</t>
+          <t>-9,61; 1,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 2,94</t>
+          <t>-7,62; 3,41</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,52; -0,31</t>
+          <t>-9,58; -0,44</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,96</t>
+          <t>-4,48; 4,01</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 7,56</t>
+          <t>-1,03; 7,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,78</t>
+          <t>-5,37; 1,42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,51</t>
+          <t>-5,22; 0,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 4,39</t>
+          <t>-2,68; 3,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -1,8</t>
+          <t>-6,42; -0,51</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-31,62%</t>
+          <t>-34,54%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-49,49%</t>
+          <t>-21,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-43,05%</t>
+          <t>-28,76%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 9,65</t>
+          <t>-56,68; 9,37</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-44,41; 27,27</t>
+          <t>-43,1; 29,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-53,04; -1,94</t>
+          <t>-53,42; -3,49</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 59,95</t>
+          <t>-42,48; 59,88</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 112,8</t>
+          <t>-10,9; 113,81</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,87; -10,76</t>
+          <t>-48,54; 22,62</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,37; 17,86</t>
+          <t>-41,18; 8,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 48,88</t>
+          <t>-21,1; 40,7</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,45; -19,51</t>
+          <t>-47,06; -5,17</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,72</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 8,07</t>
+          <t>-7,65; 7,74</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 1,38</t>
+          <t>-13,26; 0,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 6,48</t>
+          <t>-7,47; 6,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 8,45</t>
+          <t>-3,13; 8,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 8,12</t>
+          <t>-4,52; 7,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 7,79</t>
+          <t>-2,8; 7,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 6,34</t>
+          <t>-2,74; 6,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 3,39</t>
+          <t>-5,93; 3,6</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 5,45</t>
+          <t>-2,32; 5,73</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-3,41%</t>
+          <t>-1,38%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 48,02</t>
+          <t>-30,95; 44,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-49,66; 8,52</t>
+          <t>-49,78; 5,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 37,49</t>
+          <t>-27,7; 37,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 70,78</t>
+          <t>-16,68; 62,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 62,48</t>
+          <t>-24,14; 58,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 64,83</t>
+          <t>-14,18; 61,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 40,44</t>
+          <t>-13,7; 42,41</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 22,0</t>
+          <t>-28,38; 23,71</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 35,82</t>
+          <t>-11,13; 37,97</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,72</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,22</t>
+          <t>-1,7; 0,23</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,05</t>
+          <t>-1,76; 0,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,6</t>
+          <t>-0,22; 1,77</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,36</t>
+          <t>-0,6; 1,26</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,86</t>
+          <t>-0,32; 1,74</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,17</t>
+          <t>-0,25; 1,44</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,58</t>
+          <t>-0,84; 0,54</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,63</t>
+          <t>-0,7; 0,65</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,13</t>
+          <t>0,03; 1,36</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 5,29</t>
+          <t>-34,05; 5,66</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 1,3</t>
+          <t>-34,56; 2,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 37,82</t>
+          <t>-4,27; 43,37</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 42,19</t>
+          <t>-13,34; 37,13</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 56,14</t>
+          <t>-7,43; 54,29</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 34,53</t>
+          <t>-5,85; 44,97</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 15,17</t>
+          <t>-18,95; 14,03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 16,44</t>
+          <t>-15,57; 16,71</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 29,43</t>
+          <t>0,57; 36,01</t>
         </is>
       </c>
     </row>
